--- a/kulcsszokutatas/babylon/Babylon_Cserep_talca_kulcsszokutatas.xlsx
+++ b/kulcsszokutatas/babylon/Babylon_Cserep_talca_kulcsszokutatas.xlsx
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="H5" s="13" t="n">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
